--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>16.79253</v>
+      </c>
+      <c r="D3" t="n">
         <v>16.24809</v>
-      </c>
-      <c r="D3" t="n">
-        <v>16.79253</v>
       </c>
       <c r="E3" t="n">
         <v>16.78363</v>
